--- a/Plan_RM_Valparaiso_2026-09-15.xlsx
+++ b/Plan_RM_Valparaiso_2026-09-15.xlsx
@@ -257,7 +257,7 @@
     <t>La Reina</t>
   </si>
   <si>
-    <t>Grupo 3 · Resto de la cartera · Nuevos KAM · sin plan escrito</t>
+    <t>Grupo 3 · Clientes retail · Nuevos KAM · sin plan escrito</t>
   </si>
   <si>
     <t>REDSALUD SANTIAGO</t>
